--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488208_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488208_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.263199999999999</v>
+        <v>9.941800000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3758</v>
+        <v>9.660399999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1126</v>
+        <v>0.2814</v>
       </c>
       <c r="G2" t="n">
         <v>4.7396</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3815</v>
+        <v>1.297</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7237</v>
+        <v>0.5609</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3422</v>
+        <v>0.7362</v>
       </c>
       <c r="V2" t="n">
         <v>4.0904</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
+          <t>J. RUIZ CORDAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.1811</v>
+        <v>2.6263</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1529</v>
+        <v>2.9436</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0282</v>
+        <v>-0.3173</v>
       </c>
       <c r="G3" t="n">
-        <v>0.525</v>
+        <v>-0.6123</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2959</v>
+        <v>1.4798</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2291</v>
+        <v>-2.092</v>
       </c>
       <c r="J3" t="n">
-        <v>1.0055</v>
+        <v>3.3754</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9226</v>
+        <v>3.3019</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0829</v>
+        <v>0.0735</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4805</v>
+        <v>-3.9877</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6267</v>
+        <v>-1.8221</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1462</v>
+        <v>-2.1656</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.4087</v>
+        <v>1.297</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.891</v>
+        <v>-0.9264</v>
       </c>
       <c r="R3" t="n">
-        <v>1.4823</v>
+        <v>2.2234</v>
       </c>
       <c r="S3" t="n">
-        <v>5.8071</v>
+        <v>1.3116</v>
       </c>
       <c r="T3" t="n">
-        <v>3.5217</v>
+        <v>0.4946</v>
       </c>
       <c r="U3" t="n">
-        <v>2.2853</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2578</v>
+        <v>0.63</v>
       </c>
       <c r="W3" t="n">
-        <v>2.5166</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2589</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RUIZ CORDAL</t>
+          <t>J. RODRIGUEZ - GUERRA SALGUEIRO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.936</v>
+        <v>2.0719</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7362</v>
+        <v>1.0531</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1998</v>
+        <v>1.0187</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.6123</v>
+        <v>0.525</v>
       </c>
       <c r="H4" t="n">
-        <v>1.4798</v>
+        <v>0.2959</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.092</v>
+        <v>0.2291</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3754</v>
+        <v>1.0055</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3019</v>
+        <v>0.9226</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0735</v>
+        <v>0.0829</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.9877</v>
+        <v>-0.4805</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.8221</v>
+        <v>-0.6267</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.1656</v>
+        <v>0.1462</v>
       </c>
       <c r="P4" t="n">
-        <v>1.297</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9264</v>
+        <v>-3.891</v>
       </c>
       <c r="R4" t="n">
-        <v>2.2234</v>
+        <v>1.4823</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6213</v>
+        <v>2.6978</v>
       </c>
       <c r="T4" t="n">
-        <v>0.2873</v>
+        <v>1.422</v>
       </c>
       <c r="U4" t="n">
-        <v>1.334</v>
+        <v>1.2758</v>
       </c>
       <c r="V4" t="n">
-        <v>0.63</v>
+        <v>1.2578</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.5166</v>
       </c>
       <c r="X4" t="n">
-        <v>0.63</v>
+        <v>-1.2589</v>
       </c>
     </row>
     <row r="5">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0411</v>
+        <v>1.0171</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5239</v>
+        <v>0.4259</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5173</v>
+        <v>0.5911</v>
       </c>
       <c r="G7" t="n">
         <v>-0.2504</v>
@@ -1000,13 +1000,13 @@
         <v>0.3706</v>
       </c>
       <c r="S7" t="n">
-        <v>0.921</v>
+        <v>0.8969</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4004</v>
+        <v>0.3025</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5205</v>
+        <v>0.5944</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. GALAN PLAZA</t>
+          <t>M. TRILLO MANGANO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0949</v>
+        <v>0.0385</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2907</v>
+        <v>0.5115</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.3856</v>
+        <v>-0.473</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.7088</v>
+        <v>0.1455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4399</v>
+        <v>0.1915</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.1487</v>
+        <v>-0.046</v>
       </c>
       <c r="J9" t="n">
-        <v>2.3487</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2243</v>
+        <v>0.09859999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1244</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-4.0575</v>
+        <v>0.0469</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7844</v>
+        <v>0.0929</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.2731</v>
+        <v>-0.046</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.9264</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0226</v>
+        <v>0.8369</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2226</v>
+        <v>0.4129</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2452</v>
+        <v>0.424</v>
       </c>
       <c r="V9" t="n">
-        <v>2.5177</v>
+        <v>-0.9439</v>
       </c>
       <c r="W9" t="n">
-        <v>2.2027</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.315</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. TRILLO MANGANO</t>
+          <t>C. GALAN PLAZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5748</v>
+        <v>-0.1387</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1198</v>
+        <v>2.3454</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6946</v>
+        <v>-2.4841</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1455</v>
+        <v>-1.7088</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1915</v>
+        <v>0.4399</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.046</v>
+        <v>-2.1487</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09859999999999999</v>
+        <v>2.3487</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09859999999999999</v>
+        <v>2.2243</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.1244</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0469</v>
+        <v>-4.0575</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0929</v>
+        <v>-1.7844</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.046</v>
+        <v>-2.2731</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2236</v>
+        <v>-0.0211</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0211</v>
+        <v>-0.1679</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2024</v>
+        <v>0.1467</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9439</v>
+        <v>2.5177</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2.2027</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.9439</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.4407</v>
+        <v>-0.9494</v>
       </c>
       <c r="E11" t="n">
-        <v>1.1109</v>
+        <v>1.3067</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5516</v>
+        <v>-2.2561</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4932</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.003</v>
+        <v>-0.5117</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5471</v>
+        <v>-0.3513</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4559</v>
+        <v>-0.1604</v>
       </c>
       <c r="V11" t="n">
         <v>0.3144</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. CASTRO DIANEZ</t>
+          <t>M. CABEZA RUEDA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.4997</v>
+        <v>-2.471</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.516</v>
+        <v>0.06519999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0164</v>
+        <v>-2.5362</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8329</v>
+        <v>-2.5861</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4996</v>
+        <v>-2.775</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.3332</v>
+        <v>0.1889</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0066</v>
+        <v>0.6038</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2577</v>
+        <v>-1.3359</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2643</v>
+        <v>1.9397</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.8263</v>
+        <v>-3.19</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7573</v>
+        <v>-1.4391</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.06900000000000001</v>
+        <v>-1.7508</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6676</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.0382</v>
+        <v>-2.7793</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3706</v>
+        <v>2.2234</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0007</v>
+        <v>0.041</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4713</v>
+        <v>0.0386</v>
       </c>
       <c r="U12" t="n">
-        <v>0.472</v>
+        <v>0.0025</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.63</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.2022</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.5722</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. CABEZA RUEDA</t>
+          <t>D. CASTRO DIANEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.5307</v>
+        <v>-2.6604</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7729</v>
+        <v>-2.8738</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7578</v>
+        <v>0.2133</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.5861</v>
+        <v>-1.8329</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.775</v>
+        <v>-0.4996</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1889</v>
+        <v>-1.3332</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6038</v>
+        <v>-1.0066</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.3359</v>
+        <v>0.2577</v>
       </c>
       <c r="L13" t="n">
-        <v>1.9397</v>
+        <v>-1.2643</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.19</v>
+        <v>-0.8263</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4391</v>
+        <v>-0.7573</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.7508</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.5558999999999999</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.7793</v>
+        <v>-2.0382</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2234</v>
+        <v>0.3706</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.0187</v>
+        <v>0.84</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.7996</v>
+        <v>0.171</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2191</v>
+        <v>0.669</v>
       </c>
       <c r="V13" t="n">
-        <v>0.63</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.2022</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.5722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.2213</v>
+        <v>-4.8695</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1975</v>
+        <v>-0.6724</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.4187</v>
+        <v>-4.1972</v>
       </c>
       <c r="G14" t="n">
         <v>-3.68</v>
@@ -1546,13 +1546,13 @@
         <v>2.594</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3863</v>
+        <v>0.738</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3194</v>
+        <v>0.4496</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0669</v>
+        <v>0.2885</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6304999999999999</v>
@@ -1579,19 +1579,19 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>7.235899999999996</v>
+        <v>7.783199999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>17.39540000000001</v>
+        <v>17.9422</v>
       </c>
       <c r="F15" t="n">
-        <v>-10.1592</v>
+        <v>-10.1594</v>
       </c>
       <c r="G15" t="n">
-        <v>-3.576999999999999</v>
+        <v>-3.577</v>
       </c>
       <c r="H15" t="n">
-        <v>2.988599999999999</v>
+        <v>2.9886</v>
       </c>
       <c r="I15" t="n">
         <v>-6.5655</v>
@@ -1624,16 +1624,16 @@
         <v>12.97</v>
       </c>
       <c r="S15" t="n">
-        <v>7.579400000000001</v>
+        <v>8.1264</v>
       </c>
       <c r="T15" t="n">
-        <v>2.785600000000001</v>
+        <v>3.3329</v>
       </c>
       <c r="U15" t="n">
-        <v>4.793500000000001</v>
+        <v>4.793699999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>7.865900000000002</v>
+        <v>7.8659</v>
       </c>
       <c r="W15" t="n">
         <v>16.3607</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>11.6025</v>
+        <v>11.8155</v>
       </c>
       <c r="E16" t="n">
-        <v>14.8757</v>
+        <v>14.6798</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.2732</v>
+        <v>-2.8643</v>
       </c>
       <c r="G16" t="n">
         <v>13.5902</v>
@@ -1702,13 +1702,13 @@
         <v>3.5205</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2992</v>
+        <v>-1.0862</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6429</v>
+        <v>-0.8387</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6564</v>
+        <v>-0.2475</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5032</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. VALVERDE PIZARRO</t>
+          <t>J. LOPEZ YUSTE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.3747</v>
+        <v>1.5458</v>
       </c>
       <c r="E17" t="n">
-        <v>0.4</v>
+        <v>2.5723</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9746</v>
+        <v>-1.0265</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.6501</v>
+        <v>0.6846</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7514999999999999</v>
+        <v>1.622</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1014</v>
+        <v>-0.9374</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4211</v>
+        <v>2.767</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5455</v>
+        <v>3.2207</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1244</v>
+        <v>-0.4537</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.229</v>
+        <v>-2.0824</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.206</v>
+        <v>-1.5987</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.023</v>
+        <v>-0.4837</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1853</v>
+        <v>2.7793</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1853</v>
+        <v>2.7793</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3644</v>
+        <v>-0.9737</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4377</v>
+        <v>-0.5086000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07340000000000001</v>
+        <v>-0.4651</v>
       </c>
       <c r="V17" t="n">
-        <v>2.2038</v>
+        <v>-0.9444</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2589</v>
+        <v>0.3139</v>
       </c>
       <c r="X17" t="n">
-        <v>0.945</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. LÓPEZ YUSTE</t>
+          <t>J. VALVERDE PIZARRO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6221</v>
+        <v>1.4801</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6221</v>
+        <v>0.498</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>0.9821</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6221</v>
+        <v>-0.6501</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6221</v>
+        <v>0.1014</v>
       </c>
       <c r="J18" t="n">
-        <v>0.6221</v>
+        <v>-0.4211</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.5455</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6221</v>
+        <v>0.1244</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>-0.229</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.206</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-0.023</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>-0.259</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-0.3398</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.0808</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.2038</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. LOPEZ YUSTE</t>
+          <t>J. LÓPEZ YUSTE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6072</v>
+        <v>0.6221</v>
       </c>
       <c r="E19" t="n">
-        <v>1.7889</v>
+        <v>0.6221</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.1817</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6846</v>
+        <v>0.6221</v>
       </c>
       <c r="H19" t="n">
-        <v>1.622</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.9374</v>
+        <v>0.6221</v>
       </c>
       <c r="J19" t="n">
-        <v>2.767</v>
+        <v>0.6221</v>
       </c>
       <c r="K19" t="n">
-        <v>3.2207</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4537</v>
+        <v>0.6221</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0824</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5987</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4837</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.7793</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.9123</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.292</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6203</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.9444</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3139</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.147</v>
+        <v>0.1716</v>
       </c>
       <c r="E21" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2017</v>
+        <v>0.2263</v>
       </c>
       <c r="G21" t="n">
         <v>0.1306</v>
@@ -2092,13 +2092,13 @@
         <v>0.1853</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1689</v>
+        <v>-0.1443</v>
       </c>
       <c r="T21" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1142</v>
+        <v>-0.0895</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5767</v>
+        <v>-0.7731</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1929</v>
+        <v>-1.2908</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6162</v>
+        <v>0.5177</v>
       </c>
       <c r="G22" t="n">
         <v>0.009900000000000001</v>
@@ -2170,13 +2170,13 @@
         <v>1.8529</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2721</v>
+        <v>-0.4685</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0373</v>
+        <v>-0.1352</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2348</v>
+        <v>-0.3333</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3144</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>L. LOPEZ CALZADA</t>
+          <t>G. MAIGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8031</v>
+        <v>-1.797</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3468</v>
+        <v>2.256</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4564</v>
+        <v>-4.053</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1195</v>
+        <v>-2.4953</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.7161</v>
+        <v>-2.1007</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8356</v>
+        <v>-0.3946</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4681</v>
+        <v>0.7765</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1718</v>
+        <v>0.4033</v>
       </c>
       <c r="L23" t="n">
-        <v>1.2963</v>
+        <v>0.3732</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3485</v>
+        <v>-3.2718</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8878</v>
+        <v>-2.504</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4607</v>
+        <v>-0.7678</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.7793</v>
+        <v>-1.8529</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1117</v>
+        <v>2.7793</v>
       </c>
       <c r="S23" t="n">
-        <v>1.0038</v>
+        <v>-0.6693</v>
       </c>
       <c r="T23" t="n">
-        <v>0.5944</v>
+        <v>-0.4442</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4093</v>
+        <v>-0.2251</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2589</v>
+        <v>0.4412</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.63</v>
+        <v>3.7766</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.6289</v>
+        <v>-3.3354</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>G. MAIGA</t>
+          <t>L. LOPEZ CALZADA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.0523</v>
+        <v>-2.8007</v>
       </c>
       <c r="E24" t="n">
-        <v>2.5498</v>
+        <v>-2.1302</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.6021</v>
+        <v>-0.6705</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.4953</v>
+        <v>0.1195</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.1007</v>
+        <v>-0.7161</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.3946</v>
+        <v>0.8356</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7765</v>
+        <v>1.4681</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4033</v>
+        <v>0.1718</v>
       </c>
       <c r="L24" t="n">
-        <v>0.3732</v>
+        <v>1.2963</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.2718</v>
+        <v>-1.3485</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.504</v>
+        <v>-0.8878</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.7678</v>
+        <v>-0.4607</v>
       </c>
       <c r="P24" t="n">
-        <v>0.9264</v>
+        <v>-1.6676</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.8529</v>
+        <v>-2.7793</v>
       </c>
       <c r="R24" t="n">
-        <v>2.7793</v>
+        <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9247</v>
+        <v>0.0062</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1504</v>
+        <v>-0.189</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7742</v>
+        <v>0.1952</v>
       </c>
       <c r="V24" t="n">
-        <v>0.4412</v>
+        <v>-1.2589</v>
       </c>
       <c r="W24" t="n">
-        <v>3.7766</v>
+        <v>-0.63</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.3354</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>F. GONZALEZ ROSCO</t>
+          <t>A. MARTINEZ AGUDO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.7588</v>
+        <v>-5.3872</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.4996</v>
+        <v>-1.4489</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.2592</v>
+        <v>-3.9384</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.4003</v>
+        <v>-1.4254</v>
       </c>
       <c r="H25" t="n">
-        <v>-2.4187</v>
+        <v>-1.5018</v>
       </c>
       <c r="I25" t="n">
-        <v>0.0185</v>
+        <v>0.0764</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.7883</v>
+        <v>1.4781</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.8298</v>
+        <v>0.6569</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0415</v>
+        <v>0.8212</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.612</v>
+        <v>-2.9035</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.589</v>
+        <v>-2.1587</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.023</v>
+        <v>-0.7448</v>
       </c>
       <c r="P25" t="n">
         <v>0.7411</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7411</v>
+        <v>2.594</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7638</v>
+        <v>-1.0527</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7113</v>
+        <v>-0.7592</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.0525</v>
+        <v>-0.2935</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.3359</v>
+        <v>-3.6503</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>-0.315</v>
       </c>
       <c r="X25" t="n">
-        <v>-3.3359</v>
+        <v>-3.3354</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A. MARTINEZ AGUDO</t>
+          <t>F. GONZALEZ ROSCO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.8592</v>
+        <v>-5.4318</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.0365</v>
+        <v>-2.4016</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.8227</v>
+        <v>-3.0302</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.4254</v>
+        <v>-2.4003</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.5018</v>
+        <v>-2.4187</v>
       </c>
       <c r="I26" t="n">
-        <v>0.0764</v>
+        <v>0.0185</v>
       </c>
       <c r="J26" t="n">
-        <v>1.4781</v>
+        <v>-1.7883</v>
       </c>
       <c r="K26" t="n">
-        <v>0.6569</v>
+        <v>-1.8298</v>
       </c>
       <c r="L26" t="n">
-        <v>0.8212</v>
+        <v>0.0415</v>
       </c>
       <c r="M26" t="n">
-        <v>-2.9035</v>
+        <v>-0.612</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.1587</v>
+        <v>-0.589</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.7448</v>
+        <v>-0.023</v>
       </c>
       <c r="P26" t="n">
         <v>0.7411</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5246</v>
+        <v>-0.4368</v>
       </c>
       <c r="T26" t="n">
-        <v>-1.3467</v>
+        <v>-0.6133999999999999</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1779</v>
+        <v>0.1766</v>
       </c>
       <c r="V26" t="n">
-        <v>-3.6503</v>
+        <v>-3.3359</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-3.3354</v>
+        <v>-3.3359</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.8613</v>
+        <v>-5.6975</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.2688</v>
+        <v>-3.4647</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.5925</v>
+        <v>-2.2329</v>
       </c>
       <c r="G27" t="n">
         <v>-4.9308</v>
@@ -2560,13 +2560,13 @@
         <v>1.8529</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.3532</v>
+        <v>-1.1894</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.715</v>
+        <v>-0.9109</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.6382</v>
+        <v>-0.2786</v>
       </c>
       <c r="V27" t="n">
         <v>-0.5038</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-7.235799999999999</v>
+        <v>-5.930099999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>10.1593</v>
+        <v>10.1594</v>
       </c>
       <c r="F28" t="n">
-        <v>-17.3953</v>
+        <v>-16.0897</v>
       </c>
       <c r="G28" t="n">
         <v>3.5771</v>
@@ -2608,7 +2608,7 @@
         <v>-2.9885</v>
       </c>
       <c r="I28" t="n">
-        <v>6.5657</v>
+        <v>6.565700000000001</v>
       </c>
       <c r="J28" t="n">
         <v>19.4283</v>
@@ -2638,13 +2638,13 @@
         <v>17.6023</v>
       </c>
       <c r="S28" t="n">
-        <v>-7.579400000000001</v>
+        <v>-6.2737</v>
       </c>
       <c r="T28" t="n">
-        <v>-4.7936</v>
+        <v>-4.7937</v>
       </c>
       <c r="U28" t="n">
-        <v>-2.7858</v>
+        <v>-1.48</v>
       </c>
       <c r="V28" t="n">
         <v>-7.8659</v>
